--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T05:34:23+08:00</t>
+    <t>2026-02-28T07:16:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T07:16:04+08:00</t>
+    <t>2026-02-28T23:13:53+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.4.1</t>
+    <t>1.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-28T23:13:53+08:00</t>
+    <t>2026-03-01T19:25:35+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-01T19:25:35+08:00</t>
+    <t>2026-03-02T02:26:08+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2375" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-02T02:26:08+08:00</t>
+    <t>2026-04-02T13:32:15+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -269,10 +269,10 @@
 </t>
   </si>
   <si>
-    <t>Measurements and simple assertions</t>
-  </si>
-  <si>
-    <t>Measurements and simple assertions made about a patient, device or other subject.</t>
+    <t>通用檢驗檢查結果或發現的測量和簡單聲明</t>
+  </si>
+  <si>
+    <t>關於患者的通用檢驗檢查結果測量和簡單聲明，包括由設備或醫護人員觀察到的發現。</t>
   </si>
   <si>
     <t>Used for simple observations such as device measurements, laboratory atomic results, vital signs, height, weight, smoking status, comments, etc.  Other resources are used to provide context for observations such as laboratory reports, etc.</t>
@@ -346,10 +346,10 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+    <t>創建此內容所依據的一組規則</t>
+  </si>
+  <si>
+    <t>構建 resource 時遵循的一系列規則的參照，在處理內容時必須理解這些規則。通常這是對 IG 所定義之特殊規則及其他 profiles 的參照。</t>
   </si>
   <si>
     <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
@@ -380,7 +380,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -520,10 +520,10 @@
 </t>
   </si>
   <si>
-    <t>Fulfills plan, proposal or order</t>
-  </si>
-  <si>
-    <t>A plan, proposal or order that is fulfilled in whole or in part by this event.  For example, a MedicationRequest may require a patient to have laboratory test performed before  it is dispensed.</t>
+    <t>檢驗檢查的依據</t>
+  </si>
+  <si>
+    <t>產生此檢驗檢查的計畫或請求。</t>
   </si>
   <si>
     <t>Allows tracing of authorization for the event and tracking whether proposals/recommendations were acted upon.</t>
@@ -549,10 +549,10 @@
 </t>
   </si>
   <si>
-    <t>Part of referenced event</t>
-  </si>
-  <si>
-    <t>A larger event of which this particular Observation is a component or step.  For example,  an observation as part of a procedure.</t>
+    <t>作為較大項目的一部分</t>
+  </si>
+  <si>
+    <t>表示此檢驗檢查是其他資源的一部分，例如：用藥給藥、調劑、用藥聲明、處置、免疫接種或影像檢查。</t>
   </si>
   <si>
     <t>To link an Observation to an Encounter use `encounter`.  See the  [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below for guidance on referencing another Observation.</t>
@@ -573,7 +573,7 @@
     <t>registered | preliminary | final | amended +</t>
   </si>
   <si>
-    <t>The status of the result value.</t>
+    <t>該項檢驗檢查的狀態。</t>
   </si>
   <si>
     <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
@@ -616,7 +616,7 @@
     <t>跌倒紀錄的類別</t>
   </si>
   <si>
-    <t>A code that classifies the general type of observation being made.</t>
+    <t>檢驗檢查的分類。</t>
   </si>
   <si>
     <t>In addition to the required category valueset, this element allows various categorization schemes based on the owner’s definition of the category and effectively multiple categories can be used at once.  The level of granularity is defined by the category concepts in the value set.</t>
@@ -704,14 +704,10 @@
     <t>CodeableConcept.coding</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
-    <t>CE/CNE/CWE subset one of the sets of component 1-3 or 4-6</t>
-  </si>
-  <si>
-    <t>CV</t>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
   </si>
   <si>
     <t>Observation.category.text</t>
@@ -748,7 +744,10 @@
 </t>
   </si>
   <si>
-    <t>Classification of  type of observation</t>
+    <t>臺灣核心分類</t>
+  </si>
+  <si>
+    <t>臺灣核心檢驗檢查分類。</t>
   </si>
   <si>
     <t>Observation.code</t>
@@ -761,10 +760,10 @@
     <t>跌倒紀錄的類型</t>
   </si>
   <si>
-    <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
+    <t>描述該檢驗檢查所測量的內容</t>
+  </si>
+  <si>
+    <t>*All* code-value and, if present, component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
   </si>
   <si>
     <t>Knowing what kind of observation is being made is essential to understanding the observation.</t>
@@ -776,10 +775,22 @@
     <t>http://hl7.org/fhir/ValueSet/observation-codes</t>
   </si>
   <si>
-    <t>CE/CNE/CWE</t>
-  </si>
-  <si>
-    <t>CD</t>
+    <t>Event.code</t>
+  </si>
+  <si>
+    <t>&lt; 363787002 |Observable entity| OR &lt; 386053000 |Evaluation procedure|</t>
+  </si>
+  <si>
+    <t>OBX-3</t>
+  </si>
+  <si>
+    <t>code</t>
+  </si>
+  <si>
+    <t>FiveWs.what[x]</t>
+  </si>
+  <si>
+    <t>116680003 |Is a|</t>
   </si>
   <si>
     <t>Observation.code.id</t>
@@ -811,7 +822,7 @@
     <t>跌倒紀錄的對象</t>
   </si>
   <si>
-    <t>The patient, or group of patients, location, or device this observation is about and into whose record the observation is placed. If the actual focus of the observation is different from the subject (or a sample of, part, or region of the subject), the `focus` element or the `code` itself specifies the actual focus of the observation.</t>
+    <t>檢驗檢查關注的主體 (如患者、群組、設備或位置)。</t>
   </si>
   <si>
     <t>One would expect this element to be a cardinality of 1..1. The only circumstance in which the subject can be missing is when the observation is made by a device that does not know the patient. In this case, the observation SHALL be matched to a patient through some context/channel matching technique, and at this point, the observation should be updated.</t>
@@ -835,7 +846,7 @@
     <t>Observation.focus</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.0.1)
 </t>
   </si>
   <si>
@@ -846,9 +857,6 @@
   </si>
   <si>
     <t>Typically, an observation is made about the subject - a patient, or group of patients, location, or device - and the distinction between the subject and what is directly measured for an observation is specified in the observation code itself ( e.g., "Blood Glucose") and does not need to be represented separately using this element.  Use `specimen` if a reference to a specimen is required.  If a code is required instead of a resource use either  `bodysite` for bodysites or the standard extension [focusCode](http://hl7.org/fhir/R4/extension-observation-focuscode.html).</t>
-  </si>
-  <si>
-    <t>OBX-3</t>
   </si>
   <si>
     <t>participation[typeCode=SBJ]</t>
@@ -865,10 +873,10 @@
 </t>
   </si>
   <si>
-    <t>Healthcare event during which this observation is made</t>
-  </si>
-  <si>
-    <t>The healthcare event  (e.g. a patient and healthcare provider interaction) during which this observation is made.</t>
+    <t>與此檢驗檢查相關的就醫事件</t>
+  </si>
+  <si>
+    <t>此檢驗檢查是在哪個就醫情境產生的。</t>
   </si>
   <si>
     <t>This will typically be the encounter the event occurred within, but some events may be initiated prior to or after the official completion of an encounter but still be tied to the context of the encounter (e.g. pre-admission laboratory tests).</t>
@@ -900,10 +908,10 @@
 </t>
   </si>
   <si>
-    <t>Clinically relevant time/time-period for observation</t>
-  </si>
-  <si>
-    <t>The time or time-period the observed value is asserted as being true. For biological subjects - e.g. human patients - this is usually called the "physiologically relevant time". This is usually either the time of the procedure or of specimen collection, but very often the source of the date/time is not known, only the date/time itself.</t>
+    <t>檢驗檢查的時間或時段</t>
+  </si>
+  <si>
+    <t>檢驗檢查進行的時間點或時間段。</t>
   </si>
   <si>
     <t>At least a date should be present unless this observation is a historical report.  For recording imprecise or "fuzzy" times (For example, a blood glucose measurement taken "after breakfast") use the [Timing](http://hl7.org/fhir/R4/datatypes.html#timing) datatype which allow the measurement to be tied to regular life events.</t>
@@ -972,10 +980,10 @@
 </t>
   </si>
   <si>
-    <t>Who is responsible for the observation</t>
-  </si>
-  <si>
-    <t>Who was responsible for asserting the observed value as "true".</t>
+    <t>負責該檢驗檢查的人員</t>
+  </si>
+  <si>
+    <t>執行或負責檢驗檢查的人員。</t>
   </si>
   <si>
     <t>May give a degree of confidence in the observation and also indicates where follow-up questions should be directed.</t>
@@ -999,7 +1007,7 @@
     <t>跌倒紀錄結果（如果有偵測到跌倒，則填入 Observed）</t>
   </si>
   <si>
-    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
+    <t>檢驗檢查或觀察的實際結果。</t>
   </si>
   <si>
     <t>An observation may have; 1)  a single value here, 2)  both a value and a set of related or component values,  or 3)  only a set of related or component values. If a value is present, the datatype for this element should be determined by Observation.code.  A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -1049,7 +1057,7 @@
     <t>Codes specifying why the result (`Observation.value[x]`) is missing.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/data-absent-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/data-absent-reason|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">obs-6
@@ -1081,7 +1089,7 @@
     <t>Codes identifying interpretations of observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-interpretation</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-interpretation|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values|</t>
@@ -1140,7 +1148,7 @@
     <t>Codes describing anatomical locations. May include laterality.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/body-site</t>
+    <t>http://hl7.org/fhir/ValueSet/body-site|4.0.1</t>
   </si>
   <si>
     <t>&lt; 123037004 |Body structure|</t>
@@ -1173,7 +1181,7 @@
     <t>Methods for simple observations.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/observation-methods</t>
+    <t>http://hl7.org/fhir/ValueSet/observation-methods|4.0.1</t>
   </si>
   <si>
     <t>OBX-17</t>
@@ -1189,10 +1197,10 @@
 </t>
   </si>
   <si>
-    <t>Specimen used for this observation</t>
-  </si>
-  <si>
-    <t>The specimen that was used when this observation was made.</t>
+    <t>檢驗檢查的檢體</t>
+  </si>
+  <si>
+    <t>進行檢驗檢查的檢體。</t>
   </si>
   <si>
     <t>Should only be used if not implicit in code found in `Observation.code`.  Observations are not made on specimens themselves; they are made on a subject, but in many cases by the means of a specimen. Note that although specimens are often involved, they are not always tracked and reported explicitly. Also note that observation resources may be used in contexts that track the specimen explicitly (e.g. Diagnostic Report).</t>
@@ -1213,7 +1221,7 @@
     <t>Observation.device</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Device|DeviceMetric)
+    <t xml:space="preserve">Reference(Device|4.0.1|DeviceMetric|4.0.1)
 </t>
   </si>
   <si>
@@ -1302,7 +1310,7 @@
     <t>Observation.referenceRange.low</t>
   </si>
   <si>
-    <t xml:space="preserve">Quantity {SimpleQuantity}
+    <t xml:space="preserve">Quantity {SimpleQuantity|4.0.1}
 </t>
   </si>
   <si>
@@ -1352,7 +1360,7 @@
     <t>Code for the meaning of a reference range.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-meaning|4.0.1</t>
   </si>
   <si>
     <t>&lt; 260245000 |Findings values| OR  @@ -1385,7 +1393,7 @@
     <t>Codes identifying the population the reference range applies to.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto</t>
+    <t>http://hl7.org/fhir/ValueSet/referencerange-appliesto|4.0.1</t>
   </si>
   <si>
     <t>Observation.referenceRange.age</t>
@@ -1426,10 +1434,10 @@
 </t>
   </si>
   <si>
-    <t>Related resource that belongs to the Observation group</t>
-  </si>
-  <si>
-    <t>This observation is a group observation (e.g. a battery, a panel of tests, a set of vital sign measurements) that includes the target as a member of the group.</t>
+    <t>包含的相關檢驗檢查</t>
+  </si>
+  <si>
+    <t>與此檢驗檢查相關聯的其他檢驗檢查或問卷回應。</t>
   </si>
   <si>
     <t>When using this element, an observation will typically have either a value or a set of related resources, although both may be present in some cases.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.  Note that a system may calculate results from [QuestionnaireResponse](http://hl7.org/fhir/R4/questionnaireresponse.html)  into a final score and represent the score as an Observation.</t>
@@ -1448,10 +1456,10 @@
 </t>
   </si>
   <si>
-    <t>Related measurements the observation is made from</t>
-  </si>
-  <si>
-    <t>The target resource that represents a measurement from which this observation value is derived. For example, a calculated anion gap or a fetal measurement based on an ultrasound image.</t>
+    <t>觀察來源或依據</t>
+  </si>
+  <si>
+    <t>用於獲取此觀察結果的參考資源，如：來源觀察、文件引用、問卷回應等。</t>
   </si>
   <si>
     <t>All the reference choices that are listed in this element can represent clinical observations and other measurements that may be the source for a derived value.  The most common reference will be another Observation.  For a discussion on the ways Observations can assembled in groups together, see [Notes](http://hl7.org/fhir/R4/observation.html#obsgrouping) below.</t>
@@ -1500,18 +1508,15 @@
   </si>
   <si>
     <t>*All* code-value and  component.code-component.value pairs need to be taken into account to correctly understand the meaning of the observation.</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/observation-codes|4.0.1</t>
   </si>
   <si>
     <t>&lt; 363787002 |Observable entity| OR  &lt; 386053000 |Evaluation procedure|</t>
   </si>
   <si>
-    <t>code</t>
-  </si>
-  <si>
-    <t>FiveWs.what[x]</t>
-  </si>
-  <si>
     <t>Observation.component.value[x]</t>
   </si>
   <si>
@@ -1520,6 +1525,9 @@
   </si>
   <si>
     <t>Actual component result</t>
+  </si>
+  <si>
+    <t>The information determined as a result of making the observation, if the information has a simple value.</t>
   </si>
   <si>
     <t>Used when observation has a set of component observations. An observation may have both a value (e.g. an  Apgar score)  and component observations (the observations from which the Apgar score was derived). If a value is present, the datatype for this element should be determined by Observation.code. A CodeableConcept with just a text would be used instead of a string if the field was usually coded, or if the type associated with the Observation.code defines a coded value.  For additional guidance, see the [Notes section](http://hl7.org/fhir/R4/observation.html#notes) below.</t>
@@ -3982,7 +3990,7 @@
         <v>20</v>
       </c>
       <c r="J18" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K18" t="s" s="2">
         <v>212</v>
@@ -4055,7 +4063,7 @@
         <v>81</v>
       </c>
       <c r="AI18" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AJ18" t="s" s="2">
         <v>104</v>
@@ -4067,10 +4075,10 @@
         <v>20</v>
       </c>
       <c r="AM18" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN18" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN18" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO18" t="s" s="2">
         <v>20</v>
@@ -4081,10 +4089,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4110,16 +4118,16 @@
         <v>201</v>
       </c>
       <c r="L19" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M19" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M19" t="s" s="2">
+      <c r="N19" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>20</v>
@@ -4168,7 +4176,7 @@
         <v>20</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>80</v>
@@ -4189,10 +4197,10 @@
         <v>20</v>
       </c>
       <c r="AM19" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AN19" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AN19" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AO19" t="s" s="2">
         <v>20</v>
@@ -4203,13 +4211,13 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="B20" t="s" s="2">
         <v>189</v>
       </c>
       <c r="C20" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="D20" t="s" s="2">
         <v>20</v>
@@ -4231,13 +4239,13 @@
         <v>20</v>
       </c>
       <c r="K20" t="s" s="2">
+        <v>231</v>
+      </c>
+      <c r="L20" t="s" s="2">
         <v>232</v>
       </c>
-      <c r="L20" t="s" s="2">
+      <c r="M20" t="s" s="2">
         <v>233</v>
-      </c>
-      <c r="M20" t="s" s="2">
-        <v>192</v>
       </c>
       <c r="N20" t="s" s="2">
         <v>193</v>
@@ -4348,7 +4356,7 @@
         <v>20</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K21" t="s" s="2">
         <v>190</v>
@@ -4421,36 +4429,36 @@
         <v>92</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AJ21" t="s" s="2">
         <v>104</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>20</v>
+        <v>242</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>20</v>
+        <v>243</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="AN21" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="AO21" t="s" s="2">
-        <v>20</v>
+        <v>246</v>
       </c>
       <c r="AP21" t="s" s="2">
-        <v>20</v>
+        <v>247</v>
       </c>
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4565,10 +4573,10 @@
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4683,10 +4691,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4706,7 +4714,7 @@
         <v>20</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>20</v>
+        <v>93</v>
       </c>
       <c r="K24" t="s" s="2">
         <v>212</v>
@@ -4731,7 +4739,7 @@
         <v>20</v>
       </c>
       <c r="S24" t="s" s="2">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="T24" t="s" s="2">
         <v>20</v>
@@ -4779,7 +4787,7 @@
         <v>81</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>219</v>
+        <v>20</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>104</v>
@@ -4791,10 +4799,10 @@
         <v>20</v>
       </c>
       <c r="AM24" t="s" s="2">
+        <v>219</v>
+      </c>
+      <c r="AN24" t="s" s="2">
         <v>220</v>
-      </c>
-      <c r="AN24" t="s" s="2">
-        <v>221</v>
       </c>
       <c r="AO24" t="s" s="2">
         <v>20</v>
@@ -4805,10 +4813,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4834,16 +4842,16 @@
         <v>201</v>
       </c>
       <c r="L25" t="s" s="2">
+        <v>222</v>
+      </c>
+      <c r="M25" t="s" s="2">
         <v>223</v>
       </c>
-      <c r="M25" t="s" s="2">
+      <c r="N25" t="s" s="2">
         <v>224</v>
       </c>
-      <c r="N25" t="s" s="2">
+      <c r="O25" t="s" s="2">
         <v>225</v>
-      </c>
-      <c r="O25" t="s" s="2">
-        <v>226</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>20</v>
@@ -4892,7 +4900,7 @@
         <v>20</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>80</v>
@@ -4913,10 +4921,10 @@
         <v>20</v>
       </c>
       <c r="AM25" t="s" s="2">
+        <v>227</v>
+      </c>
+      <c r="AN25" t="s" s="2">
         <v>228</v>
-      </c>
-      <c r="AN25" t="s" s="2">
-        <v>229</v>
       </c>
       <c r="AO25" t="s" s="2">
         <v>20</v>
@@ -4927,10 +4935,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4953,19 +4961,19 @@
         <v>93</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>20</v>
@@ -5014,7 +5022,7 @@
         <v>20</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>80</v>
@@ -5029,19 +5037,19 @@
         <v>104</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AN26" t="s" s="2">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="AO26" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AP26" t="s" s="2">
         <v>20</v>
@@ -5049,10 +5057,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5075,16 +5083,16 @@
         <v>93</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
@@ -5134,7 +5142,7 @@
         <v>20</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>80</v>
@@ -5155,13 +5163,13 @@
         <v>20</v>
       </c>
       <c r="AM27" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="AO27" t="s" s="2">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="AP27" t="s" s="2">
         <v>20</v>
@@ -5169,14 +5177,14 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
@@ -5195,19 +5203,19 @@
         <v>93</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>268</v>
+        <v>271</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>272</v>
+        <v>275</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>20</v>
@@ -5256,7 +5264,7 @@
         <v>20</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>80</v>
@@ -5271,19 +5279,19 @@
         <v>104</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>274</v>
+        <v>277</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="AO28" t="s" s="2">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AP28" t="s" s="2">
         <v>20</v>
@@ -5291,14 +5299,14 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
@@ -5317,19 +5325,19 @@
         <v>93</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O29" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>20</v>
@@ -5366,17 +5374,17 @@
         <v>20</v>
       </c>
       <c r="AB29" t="s" s="2">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="AC29" s="2"/>
       <c r="AD29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AE29" t="s" s="2">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>80</v>
@@ -5391,19 +5399,19 @@
         <v>104</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AL29" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AN29" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AO29" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AP29" t="s" s="2">
         <v>20</v>
@@ -5411,16 +5419,16 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="C30" t="s" s="2">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="D30" t="s" s="2">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="E30" s="2"/>
       <c r="F30" t="s" s="2">
@@ -5439,19 +5447,19 @@
         <v>93</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>20</v>
@@ -5500,7 +5508,7 @@
         <v>20</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>80</v>
@@ -5515,19 +5523,19 @@
         <v>104</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AN30" t="s" s="2">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AO30" t="s" s="2">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AP30" t="s" s="2">
         <v>20</v>
@@ -5535,10 +5543,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5561,16 +5569,16 @@
         <v>93</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -5620,7 +5628,7 @@
         <v>20</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>80</v>
@@ -5641,13 +5649,13 @@
         <v>20</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="AN31" t="s" s="2">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="AO31" t="s" s="2">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="AP31" t="s" s="2">
         <v>20</v>
@@ -5655,10 +5663,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5681,17 +5689,17 @@
         <v>93</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="N32" s="2"/>
       <c r="O32" t="s" s="2">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>20</v>
@@ -5740,7 +5748,7 @@
         <v>20</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>80</v>
@@ -5755,19 +5763,19 @@
         <v>104</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="AL32" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="AO32" t="s" s="2">
-        <v>309</v>
+        <v>312</v>
       </c>
       <c r="AP32" t="s" s="2">
         <v>20</v>
@@ -5775,10 +5783,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5801,19 +5809,19 @@
         <v>93</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>20</v>
@@ -5842,7 +5850,7 @@
       </c>
       <c r="Y33" s="2"/>
       <c r="Z33" t="s" s="2">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>20</v>
@@ -5860,7 +5868,7 @@
         <v>20</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>80</v>
@@ -5869,7 +5877,7 @@
         <v>92</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>104</v>
@@ -5878,27 +5886,27 @@
         <v>20</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AO33" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP33" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5921,19 +5929,19 @@
         <v>20</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>20</v>
@@ -5958,13 +5966,13 @@
         <v>20</v>
       </c>
       <c r="X34" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y34" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Z34" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AA34" t="s" s="2">
         <v>20</v>
@@ -5982,7 +5990,7 @@
         <v>20</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>80</v>
@@ -5991,7 +5999,7 @@
         <v>92</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>104</v>
@@ -6006,7 +6014,7 @@
         <v>135</v>
       </c>
       <c r="AN34" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO34" t="s" s="2">
         <v>20</v>
@@ -6017,14 +6025,14 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6043,19 +6051,19 @@
         <v>20</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>20</v>
@@ -6080,13 +6088,13 @@
         <v>20</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>20</v>
@@ -6104,7 +6112,7 @@
         <v>20</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>331</v>
+        <v>334</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>80</v>
@@ -6122,27 +6130,27 @@
         <v>20</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AM35" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN35" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO35" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP35" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6165,19 +6173,19 @@
         <v>20</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>20</v>
@@ -6226,7 +6234,7 @@
         <v>20</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>80</v>
@@ -6247,10 +6255,10 @@
         <v>20</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="AO36" t="s" s="2">
         <v>20</v>
@@ -6261,10 +6269,10 @@
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6287,16 +6295,16 @@
         <v>20</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="O37" s="2"/>
       <c r="P37" t="s" s="2">
@@ -6322,13 +6330,13 @@
         <v>20</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>20</v>
@@ -6346,7 +6354,7 @@
         <v>20</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>80</v>
@@ -6364,27 +6372,27 @@
         <v>20</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="AO37" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>361</v>
+        <v>364</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6407,19 +6415,19 @@
         <v>20</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>20</v>
@@ -6444,13 +6452,13 @@
         <v>20</v>
       </c>
       <c r="X38" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Y38" t="s" s="2">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="Z38" t="s" s="2">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="AA38" t="s" s="2">
         <v>20</v>
@@ -6468,7 +6476,7 @@
         <v>20</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>80</v>
@@ -6489,10 +6497,10 @@
         <v>20</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="AO38" t="s" s="2">
         <v>20</v>
@@ -6503,10 +6511,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6529,16 +6537,16 @@
         <v>20</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -6588,7 +6596,7 @@
         <v>20</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>80</v>
@@ -6606,27 +6614,27 @@
         <v>20</v>
       </c>
       <c r="AL39" t="s" s="2">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="AM39" t="s" s="2">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="AN39" t="s" s="2">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="AO39" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP39" t="s" s="2">
-        <v>379</v>
+        <v>382</v>
       </c>
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6649,16 +6657,16 @@
         <v>20</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>382</v>
+        <v>385</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -6708,7 +6716,7 @@
         <v>20</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>80</v>
@@ -6726,27 +6734,27 @@
         <v>20</v>
       </c>
       <c r="AL40" t="s" s="2">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="AM40" t="s" s="2">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="AN40" t="s" s="2">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="AO40" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP40" t="s" s="2">
-        <v>388</v>
+        <v>391</v>
       </c>
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6769,19 +6777,19 @@
         <v>20</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>391</v>
+        <v>394</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>20</v>
@@ -6830,7 +6838,7 @@
         <v>20</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>389</v>
+        <v>392</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>80</v>
@@ -6842,7 +6850,7 @@
         <v>20</v>
       </c>
       <c r="AJ41" t="s" s="2">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="AK41" t="s" s="2">
         <v>20</v>
@@ -6851,10 +6859,10 @@
         <v>20</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AN41" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AO41" t="s" s="2">
         <v>20</v>
@@ -6865,10 +6873,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>398</v>
+        <v>401</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6894,10 +6902,10 @@
         <v>201</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -6983,10 +6991,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7015,7 +7023,7 @@
         <v>139</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N43" t="s" s="2">
         <v>141</v>
@@ -7103,14 +7111,14 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7132,10 +7140,10 @@
         <v>138</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N44" t="s" s="2">
         <v>141</v>
@@ -7190,7 +7198,7 @@
         <v>20</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>80</v>
@@ -7225,10 +7233,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7251,13 +7259,13 @@
         <v>20</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7308,7 +7316,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7317,7 +7325,7 @@
         <v>92</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>104</v>
@@ -7329,10 +7337,10 @@
         <v>20</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AN45" t="s" s="2">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="AO45" t="s" s="2">
         <v>20</v>
@@ -7343,10 +7351,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7369,13 +7377,13 @@
         <v>20</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7426,7 +7434,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7435,7 +7443,7 @@
         <v>92</v>
       </c>
       <c r="AI46" t="s" s="2">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="AJ46" t="s" s="2">
         <v>104</v>
@@ -7447,10 +7455,10 @@
         <v>20</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AN46" t="s" s="2">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="AO46" t="s" s="2">
         <v>20</v>
@@ -7461,10 +7469,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7487,19 +7495,19 @@
         <v>20</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7527,10 +7535,10 @@
         <v>116</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7548,7 +7556,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7566,13 +7574,13 @@
         <v>20</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>20</v>
@@ -7583,10 +7591,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7609,19 +7617,19 @@
         <v>20</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7646,13 +7654,13 @@
         <v>20</v>
       </c>
       <c r="X48" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7670,7 +7678,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7688,13 +7696,13 @@
         <v>20</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>427</v>
+        <v>430</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>20</v>
@@ -7705,10 +7713,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7731,17 +7739,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>438</v>
+        <v>441</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7790,7 +7798,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7814,7 +7822,7 @@
         <v>20</v>
       </c>
       <c r="AN49" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="AO49" t="s" s="2">
         <v>20</v>
@@ -7825,10 +7833,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7854,10 +7862,10 @@
         <v>201</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7908,7 +7916,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7929,10 +7937,10 @@
         <v>20</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>413</v>
+        <v>416</v>
       </c>
       <c r="AN50" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="AO50" t="s" s="2">
         <v>20</v>
@@ -7943,10 +7951,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7969,16 +7977,16 @@
         <v>93</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8028,7 +8036,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8049,10 +8057,10 @@
         <v>20</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>20</v>
@@ -8063,10 +8071,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8089,16 +8097,16 @@
         <v>93</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8148,7 +8156,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8169,10 +8177,10 @@
         <v>20</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="AO52" t="s" s="2">
         <v>20</v>
@@ -8183,10 +8191,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8209,19 +8217,19 @@
         <v>93</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8270,7 +8278,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8291,10 +8299,10 @@
         <v>20</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="AO53" t="s" s="2">
         <v>20</v>
@@ -8305,10 +8313,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8334,10 +8342,10 @@
         <v>201</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>400</v>
+        <v>403</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8423,10 +8431,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8455,7 +8463,7 @@
         <v>139</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>402</v>
+        <v>405</v>
       </c>
       <c r="N55" t="s" s="2">
         <v>141</v>
@@ -8543,14 +8551,14 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8572,10 +8580,10 @@
         <v>138</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="N56" t="s" s="2">
         <v>141</v>
@@ -8630,7 +8638,7 @@
         <v>20</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -8665,10 +8673,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8691,16 +8699,16 @@
         <v>93</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>239</v>
@@ -8728,13 +8736,13 @@
         <v>20</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="Y57" t="s" s="2">
         <v>240</v>
       </c>
       <c r="Z57" t="s" s="2">
-        <v>241</v>
+        <v>475</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>20</v>
@@ -8752,7 +8760,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>92</v>
@@ -8770,16 +8778,16 @@
         <v>20</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>472</v>
+        <v>476</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>264</v>
+        <v>244</v>
       </c>
       <c r="AN57" t="s" s="2">
-        <v>473</v>
+        <v>245</v>
       </c>
       <c r="AO57" t="s" s="2">
-        <v>474</v>
+        <v>246</v>
       </c>
       <c r="AP57" t="s" s="2">
         <v>20</v>
@@ -8787,10 +8795,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8813,19 +8821,19 @@
         <v>93</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>312</v>
+        <v>480</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="O58" t="s" s="2">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="P58" t="s" s="2">
         <v>20</v>
@@ -8874,7 +8882,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8892,27 +8900,27 @@
         <v>20</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="AN58" t="s" s="2">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="AO58" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP58" t="s" s="2">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8935,19 +8943,19 @@
         <v>20</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="O59" t="s" s="2">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>20</v>
@@ -8972,13 +8980,13 @@
         <v>20</v>
       </c>
       <c r="X59" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>20</v>
@@ -8996,7 +9004,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9005,7 +9013,7 @@
         <v>92</v>
       </c>
       <c r="AI59" t="s" s="2">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="AJ59" t="s" s="2">
         <v>104</v>
@@ -9020,7 +9028,7 @@
         <v>135</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="AO59" t="s" s="2">
         <v>20</v>
@@ -9031,14 +9039,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -9057,19 +9065,19 @@
         <v>20</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="O60" t="s" s="2">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>20</v>
@@ -9094,13 +9102,13 @@
         <v>20</v>
       </c>
       <c r="X60" t="s" s="2">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="Y60" t="s" s="2">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="Z60" t="s" s="2">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>20</v>
@@ -9118,7 +9126,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9136,27 +9144,27 @@
         <v>20</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="AO60" t="s" s="2">
         <v>20</v>
       </c>
       <c r="AP60" t="s" s="2">
-        <v>342</v>
+        <v>345</v>
       </c>
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9182,16 +9190,16 @@
         <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>394</v>
+        <v>397</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>20</v>
@@ -9240,7 +9248,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9261,10 +9269,10 @@
         <v>20</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>396</v>
+        <v>399</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AO61" t="s" s="2">
         <v>20</v>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T13:32:15+08:00</t>
+    <t>2026-04-03T21:17:06+08:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
+++ b/docs/StructureDefinition-LTCObservationFallingHistory.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-03T21:17:06+08:00</t>
+    <t>2026-06-25T08:48:04+08:00</t>
   </si>
   <si>
     <t>Publisher</t>
